--- a/artfynd/A 10096-2022 artfynd.xlsx
+++ b/artfynd/A 10096-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10096-2022 artfynd.xlsx
+++ b/artfynd/A 10096-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>304586</v>
       </c>
       <c r="B2" t="n">
-        <v>77997</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489224.9121092653</v>
+        <v>489225</v>
       </c>
       <c r="R2" t="n">
-        <v>6224827.163502272</v>
+        <v>6224827</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2005-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,65 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76177766</v>
+        <v>99776702</v>
       </c>
       <c r="B3" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>6436</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Oxhaga Öst fd stenbrott, Munkahusviken, Bl</t>
+          <t>KARLSHAMN STILLERYD 2:49 m.fl, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489255.3465022261</v>
+        <v>489224</v>
       </c>
       <c r="R3" t="n">
-        <v>6224729.11345949</v>
+        <v>6224923</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,15 +866,124 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>76177766</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oxhaga Öst fd stenbrott, Munkahusviken, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489255</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6224729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-02-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-02-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Ulf Oscarsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Ulf Oscarsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10096-2022 artfynd.xlsx
+++ b/artfynd/A 10096-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/304586</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99776702</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,8 +999,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76177766</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>